--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -27314,6 +27314,154 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>6</v>
+      </c>
+      <c r="O159" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27347,7 +27495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -27430,7 +27578,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -27440,7 +27588,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -27492,7 +27640,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2164</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>23</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>23</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.2553343225503059</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>13</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.2312451922123379</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2146,9 +2131,6 @@
       <c r="O10" t="n">
         <v>15</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.2653463738693259</v>
       </c>
@@ -2791,7 +2773,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2938,9 +2920,6 @@
       <c r="O14" t="n">
         <v>30</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2803464128485004</v>
       </c>
@@ -4814,9 +4793,6 @@
       <c r="O26" t="n">
         <v>22</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5207,9 +5183,6 @@
       <c r="O28" t="n">
         <v>13</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.1443193997023468</v>
       </c>
@@ -5355,9 +5328,6 @@
       <c r="O29" t="n">
         <v>3</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -5751,9 +5721,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5899,9 +5866,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6047,9 +6011,6 @@
       <c r="O33" t="n">
         <v>7</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.1238283078056854</v>
       </c>
@@ -6692,7 +6653,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -6839,9 +6800,6 @@
       <c r="O37" t="n">
         <v>15</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.1401732064242502</v>
       </c>
@@ -8567,9 +8525,6 @@
       <c r="O48" t="n">
         <v>16</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8960,9 +8915,6 @@
       <c r="O50" t="n">
         <v>19</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -9108,9 +9060,6 @@
       <c r="O51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -9504,9 +9453,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9652,9 +9598,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9800,9 +9743,6 @@
       <c r="O55" t="n">
         <v>14</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.2476566156113709</v>
       </c>
@@ -10445,7 +10385,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -10592,9 +10532,6 @@
       <c r="O59" t="n">
         <v>27</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.2523117715636503</v>
       </c>
@@ -12172,9 +12109,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -12320,9 +12254,6 @@
       <c r="O70" t="n">
         <v>17</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12713,9 +12644,6 @@
       <c r="O72" t="n">
         <v>14</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -12861,9 +12789,6 @@
       <c r="O73" t="n">
         <v>3</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -13257,9 +13182,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -13405,9 +13327,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13553,9 +13472,6 @@
       <c r="O77" t="n">
         <v>11</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1945873408375057</v>
       </c>
@@ -13949,9 +13865,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -14198,7 +14111,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -14345,9 +14258,6 @@
       <c r="O81" t="n">
         <v>14</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.1308283259959668</v>
       </c>
@@ -15925,9 +15835,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -16073,9 +15980,6 @@
       <c r="O92" t="n">
         <v>31</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16466,9 +16370,6 @@
       <c r="O94" t="n">
         <v>17</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -16614,9 +16515,6 @@
       <c r="O95" t="n">
         <v>2</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -17010,9 +16908,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17158,9 +17053,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17306,9 +17198,6 @@
       <c r="O99" t="n">
         <v>13</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.2299668573534158</v>
       </c>
@@ -17702,9 +17591,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -17951,7 +17837,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18098,9 +17984,6 @@
       <c r="O103" t="n">
         <v>19</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.1775527281373836</v>
       </c>
@@ -19826,9 +19709,6 @@
       <c r="O114" t="n">
         <v>39</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -19974,9 +19854,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20122,9 +19999,6 @@
       <c r="O116" t="n">
         <v>14</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -20270,9 +20144,6 @@
       <c r="O117" t="n">
         <v>3</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -20666,9 +20537,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -20814,9 +20682,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -20962,9 +20827,6 @@
       <c r="O121" t="n">
         <v>10</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.1768975825795506</v>
       </c>
@@ -21358,9 +21220,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -21607,7 +21466,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -21754,9 +21613,6 @@
       <c r="O125" t="n">
         <v>30</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.2803464128485004</v>
       </c>
@@ -22150,9 +22006,6 @@
       <c r="O127" t="n">
         <v>8</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -22298,9 +22151,6 @@
       <c r="O128" t="n">
         <v>39</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.0111736487178006</v>
       </c>
@@ -22446,9 +22296,6 @@
       <c r="O129" t="n">
         <v>11</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.00898489248322343</v>
       </c>
@@ -22594,9 +22441,6 @@
       <c r="O130" t="n">
         <v>53</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.01518470210367774</v>
       </c>
@@ -22742,9 +22586,6 @@
       <c r="O131" t="n">
         <v>12</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.009801700890789196</v>
       </c>
@@ -22890,9 +22731,6 @@
       <c r="O132" t="n">
         <v>44</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.01260616778418529</v>
       </c>
@@ -23038,9 +22876,6 @@
       <c r="O133" t="n">
         <v>8</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -23186,9 +23021,6 @@
       <c r="O134" t="n">
         <v>53</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.01518470210367774</v>
       </c>
@@ -23334,9 +23166,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -23482,9 +23311,6 @@
       <c r="O136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -23878,9 +23704,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -24026,9 +23849,6 @@
       <c r="O139" t="n">
         <v>9</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.1592078243215956</v>
       </c>
@@ -24422,9 +24242,6 @@
       <c r="O141" t="n">
         <v>19</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.1775527281373836</v>
       </c>
@@ -24818,9 +24635,6 @@
       <c r="O143" t="n">
         <v>8</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -24966,9 +24780,6 @@
       <c r="O144" t="n">
         <v>42</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -25114,9 +24925,6 @@
       <c r="O145" t="n">
         <v>8</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -25262,9 +25070,6 @@
       <c r="O146" t="n">
         <v>50</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01432519066384693</v>
       </c>
@@ -25410,9 +25215,6 @@
       <c r="O147" t="n">
         <v>13</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.01061850929835496</v>
       </c>
@@ -25558,9 +25360,6 @@
       <c r="O148" t="n">
         <v>35</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.01002763346469285</v>
       </c>
@@ -25706,9 +25505,6 @@
       <c r="O149" t="n">
         <v>9</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.007351275668091897</v>
       </c>
@@ -25854,9 +25650,6 @@
       <c r="O150" t="n">
         <v>49</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.01403868685056999</v>
       </c>
@@ -26002,9 +25795,6 @@
       <c r="O151" t="n">
         <v>5</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -26150,9 +25940,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -26293,16 +26080,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O153" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R153" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26455,10 +26239,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -26694,9 +26478,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -26837,16 +26618,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26999,10 +26777,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -27238,9 +27016,6 @@
       <c r="O158" t="n">
         <v>33</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.009454625838138971</v>
       </c>
@@ -27386,9 +27161,6 @@
       <c r="O159" t="n">
         <v>6</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.004900850445394598</v>
       </c>
@@ -27459,6 +27231,151 @@
       <c r="BC159" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>41</v>
+      </c>
+      <c r="O160" t="n">
+        <v>41</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.01174665634435448</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27495,7 +27412,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -27578,7 +27495,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -27588,7 +27505,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -27640,7 +27557,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2170</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -26080,13 +26080,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R153" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26239,10 +26239,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -12249,10 +12249,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -12405,10 +12405,10 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -15975,10 +15975,10 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O92" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16131,10 +16131,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O93" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -19955,12 +19955,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -19994,81 +19994,92 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="O116" t="n">
-        <v>14</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.1554208919871427</v>
+        <v>27</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_HAEMOPHILUS_INFLUENZAE_ALL_TYPES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_HAEMOPHILUS_INFLUENZAE_ALL_TYPES_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20095,17 +20106,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20139,22 +20150,39 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="O117" t="n">
-        <v>3</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0.05336427512592412</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>27</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_HAEMOPHILUS_INFLUENZAE_ALL_TYPES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_HAEMOPHILUS_INFLUENZAE_ALL_TYPES_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Haemophilus Influenzae Disease, All Types, Invasive</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -20162,6 +20190,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary invasive Haemophilus influenzae disease notifications across all serotypes, combining confirmed and probable cases. The invasive-only source category is narrower than the unqualified D100 concept.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20174,12 +20260,12 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1459</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_HAEMOPHILUS_INFLUENZAE_ALL_TYPES_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -20187,47 +20273,47 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20254,17 +20340,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20298,170 +20384,81 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.1554208919871427</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -20493,12 +20490,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20532,81 +20529,95 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20633,17 +20644,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20677,81 +20688,170 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20783,12 +20883,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20822,95 +20922,81 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0.1768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20937,17 +21023,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20981,170 +21067,81 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>10</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21176,12 +21173,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21215,13 +21212,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>0.1768975825795506</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21230,7 +21227,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -21255,7 +21252,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21268,42 +21265,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21335,12 +21332,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21374,29 +21371,29 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae type b</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -21406,7 +21403,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -21421,7 +21418,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -21431,7 +21428,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -21456,17 +21453,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -21489,7 +21486,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -21502,42 +21499,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21569,12 +21566,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21608,13 +21605,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0.2803464128485004</v>
+        <v>0</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21623,7 +21620,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -21648,7 +21645,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -21661,42 +21658,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21728,12 +21725,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21767,29 +21764,29 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>Invasiv infektion med Haemophilus influenzae</t>
+          <t>Haemophilus influenzae type b</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -21799,7 +21796,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -21814,7 +21811,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -21824,7 +21821,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -21849,17 +21846,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -21882,7 +21879,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -21895,42 +21892,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21962,12 +21959,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21992,7 +21989,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22001,81 +21998,95 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O127" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="R127" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.2803464128485004</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22102,17 +22113,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22137,7 +22148,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22146,81 +22157,170 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O128" t="n">
-        <v>39</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0.0111736487178006</v>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Invasiv infektion med Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22382,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22291,13 +22391,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O129" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R129" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22427,7 +22527,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22436,13 +22536,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O130" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R130" t="n">
-        <v>0.01518470210367774</v>
+        <v>0.0111736487178006</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22572,7 +22672,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22581,13 +22681,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O131" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R131" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22717,7 +22817,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22726,13 +22826,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="O132" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="R132" t="n">
-        <v>0.01260616778418529</v>
+        <v>0.01518470210367774</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22862,7 +22962,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22871,13 +22971,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O133" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R133" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23007,7 +23107,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23016,13 +23116,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="O134" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="R134" t="n">
-        <v>0.01518470210367774</v>
+        <v>0.01260616778418529</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23122,12 +23222,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23152,22 +23252,22 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23200,42 +23300,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23267,12 +23367,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23297,104 +23397,90 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="O136" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="R136" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.01518470210367774</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23421,17 +23507,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23465,170 +23551,81 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>2</v>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AT137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV137" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23660,12 +23657,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23699,81 +23696,95 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23800,17 +23811,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23844,22 +23855,39 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O139" t="n">
-        <v>9</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.1592078243215956</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -23867,6 +23895,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23879,12 +23965,12 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -23892,47 +23978,47 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23959,17 +24045,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24003,170 +24089,81 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>9</v>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24198,12 +24195,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24237,13 +24234,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O141" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="R141" t="n">
-        <v>0.1775527281373836</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24252,7 +24249,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -24277,7 +24274,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -24290,42 +24287,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24357,12 +24354,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24396,29 +24393,29 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="O142" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>Invasiv infektion med Haemophilus influenzae</t>
+          <t>Syst. H. influenzae-sykdom</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -24443,7 +24440,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -24478,17 +24475,17 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -24511,7 +24508,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -24524,42 +24521,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24591,12 +24588,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24621,7 +24618,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24630,81 +24627,95 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O143" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="R143" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.1775527281373836</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24731,17 +24742,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24766,7 +24777,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24775,81 +24786,170 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="O144" t="n">
-        <v>42</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.01203316015763142</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Invasiv infektion med Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24911,7 +25011,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25056,7 +25156,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25065,13 +25165,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O146" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R146" t="n">
-        <v>0.01432519066384693</v>
+        <v>0.01203316015763142</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25201,7 +25301,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25210,13 +25310,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R147" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25346,7 +25446,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25355,13 +25455,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="O148" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="R148" t="n">
-        <v>0.01002763346469285</v>
+        <v>0.01432519066384693</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25491,7 +25591,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25500,13 +25600,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O149" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R149" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25636,7 +25736,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25645,13 +25745,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O150" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="R150" t="n">
-        <v>0.01403868685056999</v>
+        <v>0.01002763346469285</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25781,7 +25881,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25790,13 +25890,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R151" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25896,12 +25996,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25926,22 +26026,22 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>0.01403868685056999</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -25974,42 +26074,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26041,12 +26141,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26071,12 +26171,12 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N153" t="n">
@@ -26086,89 +26186,75 @@
         <v>5</v>
       </c>
       <c r="R153" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26195,17 +26281,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26239,170 +26325,81 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>5</v>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP154" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AT154" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV154" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26434,12 +26431,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26473,81 +26470,95 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26574,17 +26585,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26618,22 +26629,39 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O156" t="n">
-        <v>2</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.03537951651591013</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -26641,6 +26669,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26653,12 +26739,12 @@
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT156" t="n">
@@ -26666,47 +26752,47 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26733,17 +26819,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26777,170 +26863,81 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>2</v>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26972,12 +26969,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27011,81 +27008,95 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="O158" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="R158" t="n">
-        <v>0.009454625838138971</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27112,17 +27123,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27147,7 +27158,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27156,81 +27167,170 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
-        <v>6</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27292,7 +27392,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27301,13 +27401,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O160" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="R160" t="n">
-        <v>0.01174665634435448</v>
+        <v>0.009454625838138971</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27374,6 +27474,296 @@
         </is>
       </c>
       <c r="BC160" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>6</v>
+      </c>
+      <c r="O161" t="n">
+        <v>6</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>41</v>
+      </c>
+      <c r="O162" t="n">
+        <v>41</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.01174665634435448</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -27495,7 +27885,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -27505,7 +27895,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -27525,7 +27915,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -27557,7 +27947,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2215</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -26470,13 +26470,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R155" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26629,10 +26629,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -27766,6 +27766,151 @@
       <c r="BC162" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>6</v>
+      </c>
+      <c r="O163" t="n">
+        <v>6</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27802,7 +27947,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -27885,7 +28030,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -27895,7 +28040,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -27947,7 +28092,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2244</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -27008,13 +27008,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R158" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27167,10 +27167,10 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -27911,6 +27911,151 @@
       <c r="BC163" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>38</v>
+      </c>
+      <c r="O164" t="n">
+        <v>38</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27947,7 +28092,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -28030,7 +28175,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -28040,7 +28185,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -28092,7 +28237,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2251</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -24588,12 +24588,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24627,13 +24627,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1775527281373836</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -24667,7 +24667,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -24680,42 +24680,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24747,12 +24747,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24786,29 +24786,29 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>Invasiv infektion med Haemophilus influenzae</t>
+          <t>Haemophilus influenzae type b</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
@@ -24818,7 +24818,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -24843,7 +24843,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -24868,17 +24868,17 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -24901,7 +24901,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -24914,42 +24914,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24981,12 +24981,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25020,81 +25020,95 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O145" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="R145" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.1775527281373836</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25121,17 +25135,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25156,7 +25170,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25165,81 +25179,170 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="O146" t="n">
-        <v>42</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0.01203316015763142</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Invasiv infektion med Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25301,7 +25404,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25446,7 +25549,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25455,13 +25558,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O148" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R148" t="n">
-        <v>0.01432519066384693</v>
+        <v>0.01203316015763142</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25591,7 +25694,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25600,13 +25703,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O149" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R149" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25736,7 +25839,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25745,13 +25848,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="O150" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="R150" t="n">
-        <v>0.01002763346469285</v>
+        <v>0.01432519066384693</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25881,7 +25984,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25890,13 +25993,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O151" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R151" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -26026,7 +26129,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26035,13 +26138,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O152" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="R152" t="n">
-        <v>0.01403868685056999</v>
+        <v>0.01002763346469285</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26171,7 +26274,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26180,13 +26283,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O153" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R153" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26286,12 +26389,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26316,22 +26419,22 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>0.01403868685056999</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26364,42 +26467,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26431,12 +26534,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26461,104 +26564,90 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R155" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26585,17 +26674,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26629,170 +26718,81 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>6</v>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP156" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AT156" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV156" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26824,12 +26824,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26863,81 +26863,95 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26964,17 +26978,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27008,22 +27022,39 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O158" t="n">
-        <v>3</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -27031,6 +27062,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27043,12 +27132,12 @@
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -27056,47 +27145,47 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27123,17 +27212,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27167,170 +27256,81 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>3</v>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27362,12 +27362,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27401,81 +27401,95 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="O160" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="R160" t="n">
-        <v>0.009454625838138971</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27502,17 +27516,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27537,7 +27551,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -27546,81 +27560,170 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O161" t="n">
-        <v>6</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0.004900850445394598</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27682,7 +27785,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -27691,13 +27794,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O162" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="R162" t="n">
-        <v>0.01174665634435448</v>
+        <v>0.009454625838138971</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27827,7 +27930,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -27972,7 +28075,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -27981,13 +28084,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O164" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="R164" t="n">
-        <v>0.01088714490452366</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28056,6 +28159,441 @@
       <c r="BC164" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>6</v>
+      </c>
+      <c r="O165" t="n">
+        <v>6</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.004900850445394598</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>38</v>
+      </c>
+      <c r="O166" t="n">
+        <v>38</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.01088714490452366</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>14</v>
+      </c>
+      <c r="O167" t="n">
+        <v>14</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28630,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -28175,7 +28713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -28185,7 +28723,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28205,7 +28743,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -28237,7 +28775,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2290</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -34294,12 +34294,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -34372,42 +34372,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34439,12 +34439,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34478,95 +34478,81 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>0.1592078243215956</v>
+        <v>0</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34593,7 +34579,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -34642,98 +34628,23 @@
       <c r="O194" t="n">
         <v>9</v>
       </c>
+      <c r="R194" t="n">
+        <v>0.1592078243215956</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -34827,17 +34738,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34871,29 +34782,104 @@
         </is>
       </c>
       <c r="N195" t="n">
+        <v>9</v>
+      </c>
+      <c r="O195" t="n">
+        <v>9</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
         <v>1</v>
       </c>
-      <c r="O195" t="n">
-        <v>1</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0.01891260466471829</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -34911,7 +34897,7 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+          <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -34924,42 +34910,42 @@
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34986,7 +34972,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -35035,98 +35021,23 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
+      <c r="R196" t="n">
+        <v>0.01891260466471829</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -35220,17 +35131,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35264,22 +35175,39 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
-        <v>19</v>
-      </c>
-      <c r="R197" t="n">
-        <v>0.1775527281373836</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -35287,6 +35215,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly Haemophilus influenzae type b notifications; the serotype-qualified source series is narrower than unqualified D100.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35304,7 +35290,7 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+          <t>SER_NZ_HAEMOPHILUS_INFLUENZAE_TYPE_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
@@ -35317,42 +35303,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35379,7 +35365,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -35428,98 +35414,23 @@
       <c r="O198" t="n">
         <v>19</v>
       </c>
+      <c r="R198" t="n">
+        <v>0.1775527281373836</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Invasiv infektion med Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -35613,17 +35524,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35648,7 +35559,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -35657,81 +35568,170 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O199" t="n">
-        <v>8</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Invasiv infektion med Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source is invasive disease and is not assumed to be type b only.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35763,12 +35763,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35802,13 +35802,13 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="O200" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="R200" t="n">
-        <v>0.01203316015763142</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -35841,42 +35841,42 @@
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35908,12 +35908,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35938,7 +35938,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -35947,93 +35947,81 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O201" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>0.01203316015763142</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36060,7 +36048,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -36112,98 +36100,18 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -36297,17 +36205,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36332,7 +36240,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -36341,81 +36249,173 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
-        <v>8</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36447,12 +36447,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36486,13 +36486,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="O204" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="R204" t="n">
-        <v>0.01432519066384693</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -36525,42 +36525,42 @@
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36592,12 +36592,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36622,7 +36622,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36631,93 +36631,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
-      </c>
-      <c r="P205" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>0.01432519066384693</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36744,7 +36732,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -36796,98 +36784,18 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -36981,17 +36889,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37016,7 +36924,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -37025,81 +36933,173 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>13</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0.01061850929835496</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37131,12 +37131,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37170,13 +37170,13 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="O208" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="R208" t="n">
-        <v>0.01002763346469285</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
@@ -37209,42 +37209,42 @@
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37276,12 +37276,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -37306,7 +37306,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -37315,93 +37315,81 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>0.01002763346469285</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37428,7 +37416,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -37480,98 +37468,18 @@
       <c r="P210" t="n">
         <v>0</v>
       </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V210" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD210" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE210" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG210" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM210" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN210" t="b">
-        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -37665,17 +37573,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37700,7 +37608,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -37709,81 +37617,173 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>9</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37815,12 +37815,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37854,13 +37854,13 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="O212" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="R212" t="n">
-        <v>0.01403868685056999</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -37893,42 +37893,42 @@
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37960,12 +37960,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37990,7 +37990,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -37999,13 +37999,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="O213" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="R213" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.01403868685056999</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -38038,42 +38038,42 @@
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38105,12 +38105,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38144,93 +38144,81 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O214" t="n">
-        <v>0</v>
-      </c>
-      <c r="P214" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ214" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38257,7 +38245,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -38309,98 +38297,18 @@
       <c r="P215" t="n">
         <v>0</v>
       </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN215" t="b">
-        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
@@ -38494,17 +38402,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -38529,12 +38437,12 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N216" t="n">
@@ -38543,76 +38451,168 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="R216" t="n">
-        <v>0</v>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN216" t="b">
+        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38644,12 +38644,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38683,95 +38683,81 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>0.1067285502518482</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38798,7 +38784,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -38847,98 +38833,23 @@
       <c r="O218" t="n">
         <v>6</v>
       </c>
+      <c r="R218" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U218" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1459</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae,total</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN218" t="b">
-        <v>1</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
@@ -39032,17 +38943,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -39076,81 +38987,170 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae,total</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; serotype child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1459</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39182,12 +39182,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39221,95 +39221,81 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0.07075903303182025</v>
+        <v>0</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -39336,7 +39322,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -39385,98 +39371,23 @@
       <c r="O221" t="n">
         <v>4</v>
       </c>
+      <c r="R221" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U221" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_103_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>Syst. H. influenzae-sykdom</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN221" t="b">
-        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
@@ -39570,17 +39481,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -39614,81 +39525,170 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="O222" t="n">
-        <v>33</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0.009454625838138971</v>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>Syst. H. influenzae-sykdom</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ222" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic disease mapping.</t>
+        </is>
+      </c>
+      <c r="AM222" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN222" t="b">
+        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ222" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_103_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39720,12 +39720,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39750,7 +39750,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -39759,13 +39759,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O223" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="R223" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.009454625838138971</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -39798,42 +39798,42 @@
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39865,12 +39865,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -39904,93 +39904,81 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA224" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ224" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40017,7 +40005,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -40069,98 +40057,18 @@
       <c r="P225" t="n">
         <v>0</v>
       </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V225" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W225" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC225" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD225" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE225" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG225" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH225" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI225" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ225" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK225" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM225" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN225" t="b">
-        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
@@ -40254,17 +40162,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40289,7 +40197,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -40298,81 +40206,173 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
-        <v>41</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0.01174665634435448</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40404,12 +40404,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40434,7 +40434,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -40443,13 +40443,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="O227" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="R227" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.01174665634435448</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -40482,42 +40482,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40549,12 +40549,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40588,93 +40588,81 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O228" t="n">
-        <v>0</v>
-      </c>
-      <c r="P228" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA228" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40701,7 +40689,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -40753,98 +40741,18 @@
       <c r="P229" t="n">
         <v>0</v>
       </c>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W229" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X229" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y229" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB229" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD229" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE229" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG229" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK229" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM229" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN229" t="b">
-        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -40938,17 +40846,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -40973,7 +40881,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -40982,81 +40890,173 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>38</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0.01088714490452366</v>
-      </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -41088,12 +41088,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -41127,13 +41127,13 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="O231" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="R231" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.01088714490452366</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -41166,42 +41166,42 @@
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -41233,12 +41233,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41272,93 +41272,81 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O232" t="n">
-        <v>0</v>
-      </c>
-      <c r="P232" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA232" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -41385,7 +41373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -41437,98 +41425,18 @@
       <c r="P233" t="n">
         <v>0</v>
       </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="V233" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
-        </is>
-      </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae type b</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD233" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE233" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG233" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK233" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM233" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN233" t="b">
-        <v>1</v>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
@@ -41622,123 +41530,360 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae type b</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ234" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM234" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN234" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_HAEMOPHILUS_INFLUENZAE_TYPE_B; SER_SG_HIST_HAEMOPHILUS_INFLUENZAE_TYPE_B</t>
+        </is>
+      </c>
+      <c r="AT234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>haemophilus-influenzae</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>D100</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
         <is>
           <t>流感嗜血杆菌</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="K235" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N234" t="n">
+      <c r="N235" t="n">
         <v>30</v>
       </c>
-      <c r="O234" t="n">
+      <c r="O235" t="n">
         <v>30</v>
       </c>
-      <c r="R234" t="n">
+      <c r="R235" t="n">
         <v>0.008595114398308155</v>
       </c>
-      <c r="S234" t="inlineStr">
+      <c r="S235" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO234" t="inlineStr">
+      <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP234" t="inlineStr">
+      <c r="AP235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR234" t="inlineStr">
+      <c r="AR235" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS234" t="inlineStr"/>
-      <c r="AT234" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU234" t="inlineStr">
+      <c r="AS235" t="inlineStr"/>
+      <c r="AT235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU235" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV234" t="inlineStr">
+      <c r="AV235" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW234" t="inlineStr">
+      <c r="AW235" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX234" t="inlineStr">
+      <c r="AX235" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY234" t="inlineStr">
+      <c r="AY235" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ234" t="inlineStr">
+      <c r="AZ235" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA234" t="inlineStr">
+      <c r="BA235" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB234" t="inlineStr">
+      <c r="BB235" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC234" t="inlineStr">
+      <c r="BC235" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -41860,7 +42005,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -41870,7 +42015,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d100/2026-2029.xlsx
+++ b/diseases/d100/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2164,17 +2174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2390,7 +2405,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2398,17 +2413,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2945,7 +2965,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2953,17 +2973,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3179,7 +3204,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3187,17 +3212,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -6929,7 +6959,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -6937,17 +6967,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7163,7 +7198,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7171,17 +7206,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7612,7 +7652,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -7620,17 +7660,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -7846,7 +7891,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -7854,17 +7899,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8401,7 +8451,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -8409,17 +8459,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -8635,7 +8690,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8643,17 +8698,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -12237,7 +12297,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -12245,17 +12305,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -12471,7 +12536,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -12479,17 +12544,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -12920,7 +12990,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -12928,17 +12998,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -13154,7 +13229,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -13162,17 +13237,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -13709,7 +13789,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -13717,17 +13797,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS75" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -13943,7 +14028,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -13951,17 +14036,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -17936,7 +18026,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -17944,17 +18034,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -18170,7 +18265,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -18178,17 +18273,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS100" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -18619,7 +18719,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18627,17 +18727,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -18853,7 +18958,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -18861,17 +18966,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -19405,7 +19515,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -19413,17 +19523,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -19639,7 +19754,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -19647,17 +19762,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -23238,7 +23358,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
@@ -23246,17 +23366,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS129" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -23472,7 +23597,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
@@ -23480,17 +23605,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS130" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -23921,7 +24051,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -23929,17 +24059,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -24155,7 +24290,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -24163,17 +24298,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS134" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -24707,7 +24847,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -24715,17 +24855,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -24941,7 +25086,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -24949,17 +25094,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -29227,7 +29377,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
@@ -29235,17 +29385,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS163" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -29461,7 +29616,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
@@ -29469,17 +29624,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS164" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -29910,7 +30070,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
@@ -29918,17 +30078,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS167" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -30144,7 +30309,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
@@ -30152,17 +30317,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS168" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -30696,7 +30866,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -30704,17 +30874,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS171" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -30930,7 +31105,7 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
@@ -30938,17 +31113,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS172" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -33970,7 +34150,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
@@ -33978,17 +34158,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS190" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -34204,7 +34389,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
@@ -34212,17 +34397,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS191" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -34653,7 +34843,7 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
@@ -34661,17 +34851,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS194" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -34887,7 +35082,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
@@ -34895,17 +35090,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS195" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -35439,7 +35639,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
@@ -35447,17 +35647,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS198" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -35673,7 +35878,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -35681,17 +35886,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS199" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HAEMOPHILUS_INVASIVE</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -38858,7 +39068,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
@@ -38866,17 +39076,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS218" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -39092,7 +39307,7 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
@@ -39100,17 +39315,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS219" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1459</t>
         </is>
       </c>
       <c r="AT219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -39396,7 +39616,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
@@ -39404,17 +39624,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS221" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -39630,7 +39855,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
@@ -39638,17 +39863,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS222" t="inlineStr">
         <is>
           <t>SER_NO_FHI_103_MONTHLY</t>
         </is>
       </c>
       <c r="AT222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
